--- a/apps/api/data/CarbonCo_ESG_Social.xlsx
+++ b/apps/api/data/CarbonCo_ESG_Social.xlsx
@@ -23,40 +23,40 @@
     <sheet name="_Manifest" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="CC_VSME_BP1_Raison_Sociale">'VSME_Reporting'!$D$7</definedName>
-    <definedName name="CC_VSME_BP2_Secteur_NAF">'VSME_Reporting'!$D$8</definedName>
-    <definedName name="CC_VSME_BP3_ETP">'VSME_Reporting'!$D$9</definedName>
-    <definedName name="CC_VSME_BP4_CA_Net">'VSME_Reporting'!$D$10</definedName>
-    <definedName name="CC_VSME_BP5_Annee">'VSME_Reporting'!$D$11</definedName>
-    <definedName name="CC_VSME_BP6_Pays">'VSME_Reporting'!$D$12</definedName>
-    <definedName name="CC_VSME_BP7_Perimetre">'VSME_Reporting'!$D$13</definedName>
-    <definedName name="CC_VSME_E1_Scope1">'VSME_Reporting'!$D$17</definedName>
-    <definedName name="CC_VSME_E2_Scope2_LB">'VSME_Reporting'!$D$18</definedName>
-    <definedName name="CC_VSME_E3_Scope2_MB">'VSME_Reporting'!$D$19</definedName>
-    <definedName name="CC_VSME_E4_Scope3">'VSME_Reporting'!$D$20</definedName>
-    <definedName name="CC_VSME_E5_Total_GES">'VSME_Reporting'!$D$21</definedName>
-    <definedName name="CC_VSME_E6_Intensite_CA">'VSME_Reporting'!$D$22</definedName>
-    <definedName name="CC_VSME_E7_Energie_MWh">'VSME_Reporting'!$D$23</definedName>
-    <definedName name="CC_VSME_E8_Part_ENR">'VSME_Reporting'!$D$24</definedName>
-    <definedName name="CC_VSME_E9_Eau_m3">'VSME_Reporting'!$D$25</definedName>
-    <definedName name="CC_VSME_E10_Dechets_t">'VSME_Reporting'!$D$26</definedName>
-    <definedName name="CC_VSME_E11_Valorisation_Pct">'VSME_Reporting'!$D$27</definedName>
-    <definedName name="CC_VSME_E12_Plan_GES">'VSME_Reporting'!$D$28</definedName>
-    <definedName name="CC_VSME_S1_Effectif">'VSME_Reporting'!$D$32</definedName>
-    <definedName name="CC_VSME_S2_Pct_CDI">'VSME_Reporting'!$D$33</definedName>
-    <definedName name="CC_VSME_S3_Rotation_Pct">'VSME_Reporting'!$D$34</definedName>
-    <definedName name="CC_VSME_S4_LTIR">'VSME_Reporting'!$D$35</definedName>
-    <definedName name="CC_VSME_S5_Formation_h_ETP">'VSME_Reporting'!$D$36</definedName>
-    <definedName name="CC_VSME_S6_Ecart_Salaire_HF">'VSME_Reporting'!$D$37</definedName>
-    <definedName name="CC_VSME_S7_Pct_Femmes_Mgmt">'VSME_Reporting'!$D$38</definedName>
-    <definedName name="CC_VSME_S8_Diversite">'VSME_Reporting'!$D$39</definedName>
-    <definedName name="CC_VSME_S9_Dialogue_Social">'VSME_Reporting'!$D$40</definedName>
-    <definedName name="CC_VSME_S10_Litiges">'VSME_Reporting'!$D$41</definedName>
-    <definedName name="CC_VSME_G1_Anti_Corruption">'VSME_Reporting'!$D$45</definedName>
-    <definedName name="CC_VSME_G2_Formation_Ethique">'VSME_Reporting'!$D$46</definedName>
-    <definedName name="CC_VSME_G3_Whistleblowing">'VSME_Reporting'!$D$47</definedName>
-    <definedName name="CC_VSME_G4_Pct_CA_Independants">'VSME_Reporting'!$D$48</definedName>
-    <definedName name="CC_VSME_G5_Protection_Donnees">'VSME_Reporting'!$D$49</definedName>
+    <definedName name="CC_VSME_BP1_Raison_Sociale">'VSME_Reporting'!$E$7</definedName>
+    <definedName name="CC_VSME_BP2_Secteur_NAF">'VSME_Reporting'!$E$8</definedName>
+    <definedName name="CC_VSME_BP3_ETP">'VSME_Reporting'!$E$9</definedName>
+    <definedName name="CC_VSME_BP4_CA_Net">'VSME_Reporting'!$E$10</definedName>
+    <definedName name="CC_VSME_BP5_Annee">'VSME_Reporting'!$E$11</definedName>
+    <definedName name="CC_VSME_BP6_Pays">'VSME_Reporting'!$E$12</definedName>
+    <definedName name="CC_VSME_BP7_Perimetre">'VSME_Reporting'!$E$13</definedName>
+    <definedName name="CC_VSME_E1_Scope1">'VSME_Reporting'!$E$17</definedName>
+    <definedName name="CC_VSME_E2_Scope2_LB">'VSME_Reporting'!$E$18</definedName>
+    <definedName name="CC_VSME_E3_Scope2_MB">'VSME_Reporting'!$E$19</definedName>
+    <definedName name="CC_VSME_E4_Scope3">'VSME_Reporting'!$E$20</definedName>
+    <definedName name="CC_VSME_E5_Total_GES">'VSME_Reporting'!$E$21</definedName>
+    <definedName name="CC_VSME_E6_Intensite_CA">'VSME_Reporting'!$E$22</definedName>
+    <definedName name="CC_VSME_E7_Energie_MWh">'VSME_Reporting'!$E$23</definedName>
+    <definedName name="CC_VSME_E8_Part_ENR">'VSME_Reporting'!$E$24</definedName>
+    <definedName name="CC_VSME_E9_Eau_m3">'VSME_Reporting'!$E$25</definedName>
+    <definedName name="CC_VSME_E10_Dechets_t">'VSME_Reporting'!$E$26</definedName>
+    <definedName name="CC_VSME_E11_Valorisation_Pct">'VSME_Reporting'!$E$27</definedName>
+    <definedName name="CC_VSME_E12_Plan_GES">'VSME_Reporting'!$E$28</definedName>
+    <definedName name="CC_VSME_S1_Effectif">'VSME_Reporting'!$E$32</definedName>
+    <definedName name="CC_VSME_S2_Pct_CDI">'VSME_Reporting'!$E$33</definedName>
+    <definedName name="CC_VSME_S3_Rotation_Pct">'VSME_Reporting'!$E$34</definedName>
+    <definedName name="CC_VSME_S4_LTIR">'VSME_Reporting'!$E$35</definedName>
+    <definedName name="CC_VSME_S5_Formation_h_ETP">'VSME_Reporting'!$E$36</definedName>
+    <definedName name="CC_VSME_S6_Ecart_Salaire_HF">'VSME_Reporting'!$E$37</definedName>
+    <definedName name="CC_VSME_S7_Pct_Femmes_Mgmt">'VSME_Reporting'!$E$38</definedName>
+    <definedName name="CC_VSME_S8_Diversite">'VSME_Reporting'!$E$39</definedName>
+    <definedName name="CC_VSME_S9_Dialogue_Social">'VSME_Reporting'!$E$40</definedName>
+    <definedName name="CC_VSME_S10_Litiges">'VSME_Reporting'!$E$41</definedName>
+    <definedName name="CC_VSME_G1_Anti_Corruption">'VSME_Reporting'!$E$45</definedName>
+    <definedName name="CC_VSME_G2_Formation_Ethique">'VSME_Reporting'!$E$46</definedName>
+    <definedName name="CC_VSME_G3_Whistleblowing">'VSME_Reporting'!$E$47</definedName>
+    <definedName name="CC_VSME_G4_Pct_CA_Independants">'VSME_Reporting'!$E$48</definedName>
+    <definedName name="CC_VSME_G5_Protection_Donnees">'VSME_Reporting'!$E$49</definedName>
     <definedName name="CC_MAT_E1_Score_Impact">'Materialite'!$F$10</definedName>
     <definedName name="CC_MAT_E2_Score_Impact">'Materialite'!$F$11</definedName>
     <definedName name="CC_MAT_E3_Score_Impact">'Materialite'!$F$12</definedName>
